--- a/shared/mock_data.xlsx
+++ b/shared/mock_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mattc/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AAED7B3-DE3D-094C-A8DC-9879822357F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9585DB67-4F3B-8945-9FFC-62D1BCEECF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5980" yWindow="2880" windowWidth="27240" windowHeight="16180" xr2:uid="{3889CEC7-4770-F34D-88FF-0B03A5AF4CFF}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1239,127 +1239,127 @@
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
       <c r="E1" s="106" t="str">
         <f t="shared" ref="E1:AI1" si="0">TEXT(E2,"ddd")</f>
-        <v>Sat</v>
+        <v>Thu</v>
       </c>
       <c r="F1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Sun</v>
+        <v>Fri</v>
       </c>
       <c r="G1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Sat</v>
       </c>
       <c r="H1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Tue</v>
+        <v>Sun</v>
       </c>
       <c r="I1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Mon</v>
       </c>
       <c r="J1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Thu</v>
+        <v>Tue</v>
       </c>
       <c r="K1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Fri</v>
+        <v>Wed</v>
       </c>
       <c r="L1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Sat</v>
+        <v>Thu</v>
       </c>
       <c r="M1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Sun</v>
+        <v>Fri</v>
       </c>
       <c r="N1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Sat</v>
       </c>
       <c r="O1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Tue</v>
+        <v>Sun</v>
       </c>
       <c r="P1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Mon</v>
       </c>
       <c r="Q1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Thu</v>
+        <v>Tue</v>
       </c>
       <c r="R1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Fri</v>
+        <v>Wed</v>
       </c>
       <c r="S1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Sat</v>
+        <v>Thu</v>
       </c>
       <c r="T1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Sun</v>
+        <v>Fri</v>
       </c>
       <c r="U1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Sat</v>
       </c>
       <c r="V1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Tue</v>
+        <v>Sun</v>
       </c>
       <c r="W1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Mon</v>
       </c>
       <c r="X1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Thu</v>
+        <v>Tue</v>
       </c>
       <c r="Y1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Fri</v>
+        <v>Wed</v>
       </c>
       <c r="Z1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Sat</v>
+        <v>Thu</v>
       </c>
       <c r="AA1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Sun</v>
+        <v>Fri</v>
       </c>
       <c r="AB1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Sat</v>
       </c>
       <c r="AC1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Tue</v>
+        <v>Sun</v>
       </c>
       <c r="AD1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Mon</v>
       </c>
       <c r="AE1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Thu</v>
+        <v>Tue</v>
       </c>
       <c r="AF1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Fri</v>
+        <v>Wed</v>
       </c>
       <c r="AG1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Sat</v>
+        <v>Thu</v>
       </c>
       <c r="AH1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Sun</v>
+        <v>Fri</v>
       </c>
       <c r="AI1" s="106" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Sat</v>
       </c>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.2">
@@ -1373,127 +1373,127 @@
         <v>34.03</v>
       </c>
       <c r="E2" s="108">
-        <v>46235</v>
+        <v>46296</v>
       </c>
       <c r="F2" s="109">
         <f>IFERROR(IF(E2=EOMONTH(E2,0),"",E2+1),"")</f>
-        <v>46236</v>
+        <v>46297</v>
       </c>
       <c r="G2" s="109">
         <f t="shared" ref="G2:AI2" si="1">IFERROR(IF(F2=EOMONTH(F2,0),"",F2+1),"")</f>
-        <v>46237</v>
+        <v>46298</v>
       </c>
       <c r="H2" s="109">
         <f t="shared" si="1"/>
-        <v>46238</v>
+        <v>46299</v>
       </c>
       <c r="I2" s="109">
         <f t="shared" si="1"/>
-        <v>46239</v>
+        <v>46300</v>
       </c>
       <c r="J2" s="109">
         <f t="shared" si="1"/>
-        <v>46240</v>
+        <v>46301</v>
       </c>
       <c r="K2" s="109">
         <f t="shared" si="1"/>
-        <v>46241</v>
+        <v>46302</v>
       </c>
       <c r="L2" s="109">
         <f t="shared" si="1"/>
-        <v>46242</v>
+        <v>46303</v>
       </c>
       <c r="M2" s="109">
         <f t="shared" si="1"/>
-        <v>46243</v>
+        <v>46304</v>
       </c>
       <c r="N2" s="109">
         <f t="shared" si="1"/>
-        <v>46244</v>
+        <v>46305</v>
       </c>
       <c r="O2" s="109">
         <f t="shared" si="1"/>
-        <v>46245</v>
+        <v>46306</v>
       </c>
       <c r="P2" s="109">
         <f t="shared" si="1"/>
-        <v>46246</v>
+        <v>46307</v>
       </c>
       <c r="Q2" s="109">
         <f>IFERROR(IF(P2=EOMONTH(P2,0),"",P2+1),"")</f>
-        <v>46247</v>
+        <v>46308</v>
       </c>
       <c r="R2" s="109">
         <f t="shared" si="1"/>
-        <v>46248</v>
+        <v>46309</v>
       </c>
       <c r="S2" s="109">
         <f t="shared" si="1"/>
-        <v>46249</v>
+        <v>46310</v>
       </c>
       <c r="T2" s="109">
         <f t="shared" si="1"/>
-        <v>46250</v>
+        <v>46311</v>
       </c>
       <c r="U2" s="109">
         <f t="shared" si="1"/>
-        <v>46251</v>
+        <v>46312</v>
       </c>
       <c r="V2" s="109">
         <f t="shared" si="1"/>
-        <v>46252</v>
+        <v>46313</v>
       </c>
       <c r="W2" s="109">
         <f t="shared" si="1"/>
-        <v>46253</v>
+        <v>46314</v>
       </c>
       <c r="X2" s="109">
         <f t="shared" si="1"/>
-        <v>46254</v>
+        <v>46315</v>
       </c>
       <c r="Y2" s="109">
         <f t="shared" si="1"/>
-        <v>46255</v>
+        <v>46316</v>
       </c>
       <c r="Z2" s="109">
         <f t="shared" si="1"/>
-        <v>46256</v>
+        <v>46317</v>
       </c>
       <c r="AA2" s="109">
         <f t="shared" si="1"/>
-        <v>46257</v>
+        <v>46318</v>
       </c>
       <c r="AB2" s="109">
         <f t="shared" si="1"/>
-        <v>46258</v>
+        <v>46319</v>
       </c>
       <c r="AC2" s="109">
         <f t="shared" si="1"/>
-        <v>46259</v>
+        <v>46320</v>
       </c>
       <c r="AD2" s="109">
         <f t="shared" si="1"/>
-        <v>46260</v>
+        <v>46321</v>
       </c>
       <c r="AE2" s="109">
         <f t="shared" si="1"/>
-        <v>46261</v>
+        <v>46322</v>
       </c>
       <c r="AF2" s="109">
         <f t="shared" si="1"/>
-        <v>46262</v>
+        <v>46323</v>
       </c>
       <c r="AG2" s="109">
         <f t="shared" si="1"/>
-        <v>46263</v>
+        <v>46324</v>
       </c>
       <c r="AH2" s="109">
         <f t="shared" si="1"/>
-        <v>46264</v>
+        <v>46325</v>
       </c>
       <c r="AI2" s="109">
         <f t="shared" si="1"/>
-        <v>46265</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.2">
@@ -1540,7 +1540,7 @@
       <c r="AK3" s="5"/>
       <c r="AL3" s="6">
         <f>AF25</f>
-        <v>8.5299999999999994</v>
+        <v>0</v>
       </c>
       <c r="AM3" s="7"/>
       <c r="AN3" s="7"/>
@@ -1724,19 +1724,13 @@
       <c r="S9" s="30"/>
       <c r="T9" s="29"/>
       <c r="U9" s="32"/>
-      <c r="V9" s="32">
-        <v>3.5</v>
-      </c>
+      <c r="V9" s="32"/>
       <c r="W9" s="32"/>
-      <c r="X9" s="32">
-        <v>3.5</v>
-      </c>
+      <c r="X9" s="32"/>
       <c r="Y9" s="32"/>
       <c r="Z9" s="32"/>
       <c r="AA9" s="32"/>
-      <c r="AB9" s="31">
-        <v>1.53</v>
-      </c>
+      <c r="AB9" s="31"/>
       <c r="AC9" s="32"/>
       <c r="AD9" s="32"/>
       <c r="AE9" s="31"/>
@@ -1746,7 +1740,7 @@
       <c r="AI9" s="32"/>
       <c r="AJ9" s="6">
         <f>SUM(E9:AI9)</f>
-        <v>34.53</v>
+        <v>26</v>
       </c>
       <c r="AK9" s="20"/>
       <c r="AL9" s="6"/>
@@ -1805,7 +1799,7 @@
       </c>
       <c r="AK10" s="20">
         <f>SUM(AJ8:AJ10)</f>
-        <v>55.53</v>
+        <v>47</v>
       </c>
       <c r="AL10" s="6"/>
       <c r="AM10" s="6"/>
@@ -1858,7 +1852,7 @@
       </c>
       <c r="AK11" s="42">
         <f>SUM(AJ8:AJ11)</f>
-        <v>55.53</v>
+        <v>47</v>
       </c>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6"/>
@@ -1987,7 +1981,7 @@
       </c>
       <c r="V13" s="48">
         <f t="shared" si="2"/>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="W13" s="48">
         <f t="shared" si="2"/>
@@ -1995,7 +1989,7 @@
       </c>
       <c r="X13" s="48">
         <f t="shared" si="2"/>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="48">
         <f t="shared" si="2"/>
@@ -2011,7 +2005,7 @@
       </c>
       <c r="AB13" s="48">
         <f t="shared" si="2"/>
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC13" s="48">
         <f t="shared" si="2"/>
@@ -2043,7 +2037,7 @@
       </c>
       <c r="AJ13" s="49">
         <f>SUM(E13:AI13)</f>
-        <v>55.53</v>
+        <v>47</v>
       </c>
       <c r="AK13" s="50"/>
       <c r="AL13" s="45"/>
@@ -2168,7 +2162,7 @@
       </c>
       <c r="V15" s="55">
         <f>V13*D7</f>
-        <v>119.105</v>
+        <v>0</v>
       </c>
       <c r="W15" s="55">
         <f>W13*D7</f>
@@ -2176,7 +2170,7 @@
       </c>
       <c r="X15" s="55">
         <f>X13*D7</f>
-        <v>119.105</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="55">
         <f>Y13*D7</f>
@@ -2192,7 +2186,7 @@
       </c>
       <c r="AB15" s="55">
         <f>AB13*D7</f>
-        <v>52.065899999999999</v>
+        <v>0</v>
       </c>
       <c r="AC15" s="55">
         <f>AC13*D7</f>
@@ -2224,11 +2218,11 @@
       </c>
       <c r="AJ15" s="57">
         <f>SUM(E15:AI15)</f>
-        <v>1889.6858999999999</v>
+        <v>1599.4099999999999</v>
       </c>
       <c r="AK15" s="42">
         <f>AJ13*D7</f>
-        <v>1889.6859000000002</v>
+        <v>1599.41</v>
       </c>
       <c r="AL15" s="6"/>
       <c r="AM15" s="6"/>
@@ -2489,7 +2483,7 @@
       </c>
       <c r="V18" s="6">
         <f>V9*D7</f>
-        <v>119.105</v>
+        <v>0</v>
       </c>
       <c r="W18" s="6">
         <f>W9*D7</f>
@@ -2497,7 +2491,7 @@
       </c>
       <c r="X18" s="6">
         <f>X9*D7</f>
-        <v>119.105</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="6">
         <f>Y9*D7</f>
@@ -2513,7 +2507,7 @@
       </c>
       <c r="AB18" s="6">
         <f>AB9*D7</f>
-        <v>52.065899999999999</v>
+        <v>0</v>
       </c>
       <c r="AC18" s="6">
         <f>AC9*D7</f>
@@ -2763,7 +2757,7 @@
       </c>
       <c r="V20" s="6">
         <f t="shared" si="3"/>
-        <v>119.105</v>
+        <v>0</v>
       </c>
       <c r="W20" s="6">
         <f t="shared" si="3"/>
@@ -2771,7 +2765,7 @@
       </c>
       <c r="X20" s="6">
         <f t="shared" si="3"/>
-        <v>119.105</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="6">
         <f t="shared" si="3"/>
@@ -2787,7 +2781,7 @@
       </c>
       <c r="AB20" s="6">
         <f t="shared" si="3"/>
-        <v>52.065899999999999</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="6">
         <f t="shared" si="3"/>
@@ -2911,7 +2905,7 @@
       <c r="AH22" s="6"/>
       <c r="AI22" s="67">
         <f>SUM(T15:AI15)</f>
-        <v>290.27589999999998</v>
+        <v>0</v>
       </c>
       <c r="AJ22" s="6"/>
       <c r="AK22" s="20"/>
@@ -2963,7 +2957,7 @@
       </c>
       <c r="AF23" s="76">
         <f>SUM(T9:AI9)</f>
-        <v>8.5299999999999994</v>
+        <v>0</v>
       </c>
       <c r="AG23" s="74">
         <f>AF23*$D$16</f>
@@ -3080,7 +3074,7 @@
       </c>
       <c r="AB25" s="88">
         <f>SUM(T15:AC15)</f>
-        <v>290.27589999999998</v>
+        <v>0</v>
       </c>
       <c r="AC25" s="80" t="s">
         <v>18</v>
@@ -3094,7 +3088,7 @@
       </c>
       <c r="AF25" s="89">
         <f>SUM(AF22:AF24)</f>
-        <v>8.5299999999999994</v>
+        <v>0</v>
       </c>
       <c r="AG25" s="90">
         <f>SUM(AG22:AG24)</f>
@@ -3143,7 +3137,7 @@
       </c>
       <c r="AG26" s="6">
         <f>SUM(T15:AI15)</f>
-        <v>290.27589999999998</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="77"/>
       <c r="AK26" s="11"/>
@@ -3205,7 +3199,7 @@
       </c>
       <c r="AK27" s="86">
         <f>AJ15-AJ27</f>
-        <v>-374.35410000000002</v>
+        <v>-664.63000000000011</v>
       </c>
       <c r="AL27" s="69"/>
       <c r="AM27" s="69"/>
@@ -3352,7 +3346,7 @@
       <c r="AE33" s="102"/>
       <c r="AF33" s="90">
         <f>SUMIFS($AF$16:AF29,$AE$16:AE29,"total")</f>
-        <v>8.5299999999999994</v>
+        <v>0</v>
       </c>
       <c r="AG33" s="90">
         <f>SUMIFS($AG$16:AG29,$AE$16:AE29,"total")</f>
